--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Serpedu_13.349164_80.035111.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Serpedu_13.349164_80.035111.xlsx
@@ -1022,6 +1022,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1029,6 +1034,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1036,6 +1046,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1043,6 +1058,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1A1A1, 1A2, 1A3, 1A4, 1A5, 1B, 1C, 1D, 1E, 1F, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1050,6 +1070,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1057,6 +1082,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1064,6 +1094,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1071,6 +1106,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1078,6 +1118,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1085,6 +1130,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1092,6 +1142,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1099,6 +1154,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1106,6 +1166,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4, 5, 6A1A, 7A1A1A1, 7A2, 7B1A, 7B1B, 7B2, 7B3A, 7B3B, 7B3C, 7B4A, 7B4B, 7B4C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1113,6 +1178,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1, 2, 3A1, 3A2, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1120,6 +1190,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1127,6 +1202,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1134,6 +1214,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1141,6 +1226,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A1A, 5A1B, 5A1C, 5A1D, 5A2, 5A3, 5B, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1148,6 +1238,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1155,6 +1250,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1162,6 +1262,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1169,6 +1274,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1176,6 +1286,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1183,6 +1298,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1190,6 +1310,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1197,6 +1322,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 11E, 12A, 12B, 13, 14, 15, 16, 2A, 2B, 3A, 3B, 3C, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1204,6 +1334,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1211,6 +1346,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1218,6 +1358,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1225,6 +1370,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1232,6 +1382,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1, 4A2, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1239,6 +1394,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 15, 16A, 16B, 17, 18, 19, 2, 20A, 20B, 20C, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1246,6 +1406,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3A1, 3A2, 3A3, 3B1, 3B2, 4</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1253,6 +1418,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1260,6 +1430,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1267,6 +1442,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1274,6 +1454,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1281,6 +1466,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10A1, 10A2, 10B, 11, 12, 13, 1A, 1B, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1288,6 +1478,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1295,6 +1490,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1A1, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 1M, 1N, 1O, 1P, 1Q, 1R, 1S, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1302,6 +1502,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1309,6 +1514,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 5A1A, 5A1B, 5A1C, 5A1D, 5A1E, 5A1F, 5A1G, 5A2, 5B1A, 5B1B, 5B2A, 5B2B</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1316,6 +1526,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 6C</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1323,6 +1538,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1330,6 +1550,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1337,6 +1562,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2, 1E, 1F, 1G, 1H, 1I, 1J, 2</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1344,6 +1574,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1351,6 +1586,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 1A, 1B, 1C, 2, 3A1A1, 3A2, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1358,6 +1598,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1365,6 +1610,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2, 1E1, 1E2, 2</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1372,6 +1622,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11A, 11B, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 1A1, 1B, 20, 21, 22, 23, 24, 2A, 2B, 3A, 3B, 4A1, 4A2, 5A1A1, 5A1B, 5A2, 5B, 6A1, 6A2, 6B, 7A, 7B, 8A1, 8A2, 8B, 9A1A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1379,6 +1634,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1A1, 1B1A2, 1B1A3, 1B1A4, 1B1B, 1B2, 1C1, 1C2, 1D, 1E, 1F, 2A1A, 2A1B, 2A2, 2A3, 2A4, 2B1A, 2B1B, 2B2, 2C1, 2C2, 2D, 2E1, 2E2, 2F, 2G1, 2G2, 2H, 2I, 2J, 2K, 2L, 2M</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1386,6 +1646,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1393,6 +1658,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>10, 100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 11, 110, 111, 112, 113, 12, 13, 14, 144, 145, 146, 147, 148, 15, 16, 17, 18, 1A1A1A, 1A1A2, 1A1B, 1A2A1, 1A2B, 1A3A, 1A3B, 1B1A1A, 1B1A2, 1B1B, 1B1C, 1B2, 1B3, 1B4, 2A1A1A1A, 2A1A2, 2A1B, 2A1C, 2A2, 2A3, 2A4, 2A5, 2A6, 2A7, 2B, 3A1A, 3A1B, 3A2A, 3A2B, 3A2C1A1A1, 3A2C2, 3A3A1, 3A3B, 3A3C, 3A4A1A1A, 3A4B, 3A5A, 3A5B, 3A6A1A1A, 3A6A2, 3A6B1A1, 3A6B2, 3A6B3, 3A6B4, 3A6B5, 3A6C1, 3A6D, 3A7A, 3A7B, 3A7C, 3A7D, 3B1, 3B2A, 3B2B, 4A1A, 4A1A2, 4A1A3, 4A1A4, 4A1B, 4A2, 4A3, 4A4, 4A5, 4B, 4C, 4D, 4E, 4F, 4G, 4H, 5, 6, 7, 70, 8, 85, 86, 87, 88, 89, 9, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1400,6 +1670,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1A1, 4A1A2, 4A1A3, 4A2, 4B1, 4B2, 4B3, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1407,6 +1682,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1414,6 +1694,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2A, 1A2B, 1A3, 1B, 20, 21, 22, 2A1A1A1, 2A2, 2A3, 2A4A1, 2A4B, 2A4C, 2A4D, 2A5, 2A6A1A, 2A6A2, 2A6B, 2B1, 2B10, 2B11, 2B1A1B, 2B1B, 2B1C, 2B1D, 2B1E, 2B2, 2B3, 2B4, 2B5, 2B6, 2B7, 2B8, 2B9, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1421,6 +1706,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2A, 2B, 3A1A1, 3A1B, 3A1C, 3A2A, 3A2B, 3A2C, 3A2D, 3B1A1, 3B1B, 3B2A, 3B2B, 3C1A, 3C1B, 3C2, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1428,6 +1718,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A10, 1A11, 1A12A1A, 1A1A1A1, 1A1A1A1A, 1A1A1B, 1A1B, 1A2A1A1, 1A2A2, 1A2B, 1A3A1A1A, 1A3B, 1A4A1, 1A5A1, 1A5B, 1A5C, 1A6A, 1A6B, 1A7A1A, 1A8A1A1, 1A8B, 1A9, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B1, 2C, 2D, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74, 75, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1435,6 +1730,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1442,6 +1742,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1449,6 +1754,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>85A, 85B</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1456,6 +1766,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1463,6 +1778,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 4</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1470,6 +1790,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1477,6 +1802,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2A1, 2A2, 2A3, 2A4, 2A5, 2A6A, 2A6B, 2A7, 2B1, 2B2, 2C, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 3K, 3L1, 3L2, 3M, 3N, 3O, 3P, 3Q, 3R, 3S</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1484,6 +1814,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1491,6 +1826,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 3F, 3G1, 3G2, 3G3, 3H1, 3H2, 3I, 3J, 3K, 3L, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1498,6 +1838,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2A, 1B2B, 1B3A, 1B3B, 1B4, 1B5A, 1B5B, 1C, 1D, 1E, 2</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1505,6 +1850,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1512,6 +1862,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1519,6 +1874,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1526,6 +1886,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1533,6 +1898,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1A4, 1B, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1540,6 +1910,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D1, 1D2, 1E, 1F, 1G, 1H, 1J, 1K, 1L, 1M, 2, 3I</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1547,11 +1922,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 2, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8</t>
         </is>
       </c>
     </row>
